--- a/config/config.xlsx
+++ b/config/config.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\B-W\config\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{253B43D9-D352-42E8-9145-6165AF69CD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>key</t>
   </si>
@@ -64,16 +58,16 @@
     <t>SUM</t>
   </si>
   <si>
-    <t>expected_principal_total</t>
-  </si>
-  <si>
-    <t>49090.97</t>
-  </si>
-  <si>
-    <t>expected_interest_total</t>
-  </si>
-  <si>
-    <t>6689.97</t>
+    <t>master_sheet</t>
+  </si>
+  <si>
+    <t>IntrestPercentage_Temp2</t>
+  </si>
+  <si>
+    <t>master_file</t>
+  </si>
+  <si>
+    <t>input/MasterDatatable_1.xlsx</t>
   </si>
   <si>
     <t>input_file_temp1</t>
@@ -104,49 +98,19 @@
   </si>
   <si>
     <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\Input</t>
-  </si>
-  <si>
-    <t>master_sheet</t>
-  </si>
-  <si>
-    <t>IntrestPercentage_Temp2</t>
-  </si>
-  <si>
-    <t>master_file</t>
-  </si>
-  <si>
-    <t>input/MasterDatatable_1.xlsx</t>
-  </si>
-  <si>
-    <t>master_share_column</t>
-  </si>
-  <si>
-    <t>BWShare</t>
-  </si>
-  <si>
-    <t>principal_col_index</t>
-  </si>
-  <si>
-    <t>client_name  </t>
-  </si>
-  <si>
-    <t>interest_col_index  </t>
-  </si>
-  <si>
-    <t>principal_col_index  </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -176,7 +140,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -509,15 +473,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="100.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.375" customWidth="1"/>
+    <col min="2" max="2" width="100.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -525,7 +489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -533,7 +497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -541,7 +505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -549,7 +513,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -557,7 +521,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -565,7 +529,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -573,86 +537,33 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="12" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="15.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -660,7 +571,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -668,7 +579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -676,7 +587,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -684,7 +595,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -692,11 +603,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:B7 A10:B11" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/config/config.xlsx
+++ b/config/config.xlsx
@@ -1,121 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>input_file</t>
-  </si>
-  <si>
-    <t>input/Consumer Collection Management, Inc. 2.xls</t>
-  </si>
-  <si>
-    <t>sheet_name</t>
-  </si>
-  <si>
-    <t>Sheet1</t>
-  </si>
-  <si>
-    <t>output_file</t>
-  </si>
-  <si>
-    <t>output/valid_remittance.xlsx</t>
-  </si>
-  <si>
-    <t>log_file</t>
-  </si>
-  <si>
-    <t>logs/app.log</t>
-  </si>
-  <si>
-    <t>log_level</t>
-  </si>
-  <si>
-    <t>INFO</t>
-  </si>
-  <si>
-    <t>rule_mode</t>
-  </si>
-  <si>
-    <t>SUM</t>
-  </si>
-  <si>
-    <t>master_sheet</t>
-  </si>
-  <si>
-    <t>IntrestPercentage_Temp2</t>
-  </si>
-  <si>
-    <t>master_file</t>
-  </si>
-  <si>
-    <t>input/MasterDatatable_1.xlsx</t>
-  </si>
-  <si>
-    <t>input_file_temp1</t>
-  </si>
-  <si>
-    <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\B-W\input\jameson and dunagan, p.c..xls</t>
-  </si>
-  <si>
-    <t>output_file_temp1</t>
-  </si>
-  <si>
-    <t>output/temp1_sheet.xlsx</t>
-  </si>
-  <si>
-    <t>MasterDatatable</t>
-  </si>
-  <si>
-    <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\MasterDatatable\MasterDatatable_1.xlsx</t>
-  </si>
-  <si>
-    <t>output_template1</t>
-  </si>
-  <si>
-    <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\Output\Output.xlsx</t>
-  </si>
-  <si>
-    <t>input_folder_temp1</t>
-  </si>
-  <si>
-    <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\Input</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -134,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -473,137 +444,208 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="21.375" customWidth="1"/>
-    <col min="2" max="2" width="100.625" customWidth="1"/>
+    <col width="21.375" customWidth="1" min="1" max="1"/>
+    <col width="100.625" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="15.75" customHeight="1" spans="1:1" x14ac:dyDescent="0.25"/>
-    <row r="16" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>input_file</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>input/Consumer Collection Management, Inc. 2.xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sheet_name</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sheet1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>output_file</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>output/valid_remittance.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>log_file</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>logs/app.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>log_level</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rule_mode</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>master_sheet</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IntrestPercentage_Temp2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>master_file</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>input/MasterDatatable_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1"/>
+    <row r="11" ht="15.75" customHeight="1"/>
+    <row r="12" ht="15.75" customHeight="1"/>
+    <row r="13" ht="15.75" customHeight="1"/>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>input_file_temp1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\B-W\input\jameson and dunagan, p.c..xls</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>output_file_temp1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>output/temp1_sheet.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MasterDatatable</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\MasterDatatable\MasterDatatable_1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>output_template1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\Output\Output.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>input_folder_temp1</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C:\Users\Admin\OneDrive - StayAhead\Documents\Projects\B&amp;W\Combined\Input</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>output_template_temp2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C:\Users\Admin\Downloads\OutputFile_Temp2.xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
